--- a/output/full_scan/batch_seq7_2026-10-29.xlsx
+++ b/output/full_scan/batch_seq7_2026-10-29.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>820.4363710227007</v>
+        <v>930.4363710227007</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>341</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>72.16252424848622</v>
+        <v>72.16252419555782</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16.51481511410674</v>
+        <v>16.51481539821002</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>4.643637102270064</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.527979865040942</v>
+        <v>2.527979866723004</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6782</v>
+        <v>6581</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>694.6172440222133</v>
+        <v>788.9862071416209</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>269</v>
+        <v>110</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.9785156314417</v>
+        <v>59.6957004881474</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>38.14630484546433</v>
+        <v>30.03754505143673</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.7378201259137203</v>
+        <v>0.6951856851140414</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.952794198706391</v>
+        <v>0.1943858124018054</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6491</v>
+        <v>6538</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>680.6454207317578</v>
+        <v>778.5976549732736</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>422.5</v>
+        <v>316</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>57.43162594337834</v>
+        <v>50.62285521941998</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34.82618974845953</v>
+        <v>24.03471525415622</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3925734389751082</v>
+        <v>1.835820785755272</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.6130349743148908</v>
+        <v>-3.513550212710976</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6811</v>
+        <v>6782</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>679.6212778720214</v>
+        <v>774.6172440222133</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>58.73158257580291</v>
+        <v>64.97851562664616</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>40.86294864715112</v>
+        <v>38.14630475290125</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5174237724233018</v>
+        <v>0.7378201259137203</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2904343435258827</v>
+        <v>1.95279419912689</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6538</v>
+        <v>6756</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>668.5976549732736</v>
+        <v>766.6449347985362</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>316</v>
+        <v>132.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>50.62285521896783</v>
+        <v>76.31966108900626</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24.03471520737083</v>
+        <v>33.50383295632112</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.835820785755272</v>
+        <v>3.658349626911945</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-3.513550212682925</v>
+        <v>3.163057147589127</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6756</v>
+        <v>6491</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>666.6449347985362</v>
+        <v>760.6454207317578</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>132.5</v>
+        <v>422.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>76.31966109208079</v>
+        <v>57.43162597904326</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33.50383298086055</v>
+        <v>34.82618971600114</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.658349626911945</v>
+        <v>0.3925734389751082</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.163057147420911</v>
+        <v>0.6130349741747256</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6689</v>
+        <v>6811</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>664.3428842725009</v>
+        <v>734.6212778720214</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>279</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.81208360790253</v>
+        <v>58.73158243741356</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>39.31014626640912</v>
+        <v>40.86294869782923</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.758888406134507</v>
+        <v>0.5174237724233018</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.7159865998416208</v>
+        <v>-0.2904343421241791</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6672</v>
+        <v>6805</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>642.735107344593</v>
+        <v>708.0326068975079</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>566</v>
+        <v>2425</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.27967421981321</v>
+        <v>55.79369719795432</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>59.4597906938174</v>
+        <v>25.84930346115041</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.518465786947482</v>
+        <v>0.7390993123783484</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-6.092636194664578</v>
+        <v>-0.2045176721438935</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6581</v>
+        <v>6690</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>623.9862071416208</v>
+        <v>690.3218065943786</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>110</v>
+        <v>187.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>59.69570059739236</v>
+        <v>58.67722589077529</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30.03754507146883</v>
+        <v>42.02815376039833</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6951856851140414</v>
+        <v>0.8067314174838168</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.194385812121466</v>
+        <v>0.8051842665522484</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6532</v>
+        <v>6715</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>618.4811791798204</v>
+        <v>663.9284662534567</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>114</v>
+        <v>482.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>51.9741330664712</v>
+        <v>54.05384315655924</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>43.20706086540079</v>
+        <v>28.65947284898655</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.4128331156998558</v>
+        <v>0.7910278331803009</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-1.102100447104592</v>
+        <v>-6.709614596209335</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6690</v>
+        <v>6719</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>610.3218065943786</v>
+        <v>645.0480896799882</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>187.5</v>
+        <v>190</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.67722594510091</v>
+        <v>55.84269507453929</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>42.02815373296819</v>
+        <v>15.13119744272564</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.8067314174838168</v>
+        <v>4.376599059544187</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.805184265711226</v>
+        <v>0.5179646450645725</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6834</v>
+        <v>6526</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>599.1968388893052</v>
+        <v>638.5928689276398</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>125</v>
+        <v>776</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>49.28907528351598</v>
+        <v>51.95961639462811</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>43.20715137680494</v>
+        <v>30.23722715406664</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.2728104723038061</v>
+        <v>0.4853442381153842</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-3.139393722355516</v>
+        <v>-9.074148779439536</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6526</v>
+        <v>6505</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>593.5928689276398</v>
+        <v>596.8363850374226</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>776</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>51.9596163851702</v>
+        <v>47.39729662011832</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30.23722702461743</v>
+        <v>49.5182536550031</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.4853442381153842</v>
+        <v>0.5041689005788424</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-9.074148783084013</v>
+        <v>-2.329543879299013</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6715</v>
+        <v>6689</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>583.9284662534567</v>
+        <v>594.3428842725009</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>482.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>54.05384315816809</v>
+        <v>57.81208364178667</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.65947287671103</v>
+        <v>39.31014624094934</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7910278331803009</v>
+        <v>1.758888406134507</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-6.709614596629788</v>
+        <v>0.715986599673412</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6695</v>
+        <v>6672</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>576.3877852806575</v>
+        <v>582.7351073445931</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>53.7</v>
+        <v>566</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.1781992288817</v>
+        <v>61.27967420097207</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>23.48028617569829</v>
+        <v>59.45979081232154</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.8440539522246153</v>
+        <v>1.518465786947482</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.2258430188159872</v>
+        <v>-6.09263619270223</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6588</v>
+        <v>6807</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>566.748575831626</v>
+        <v>573.2861671890697</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>88.7</v>
+        <v>33.95</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>35.02041863334772</v>
+        <v>52.18701361891074</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26.49141113835682</v>
+        <v>8.019051950845274</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.3089412958147158</v>
+        <v>0.3293626832079926</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>3</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.366595517878967</v>
+        <v>0.47220054893696</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6708</v>
+        <v>6534</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>558.1548386911228</v>
+        <v>560.1337551712395</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>58.42909328110042</v>
+        <v>49.17774951274426</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>25.50194434070382</v>
+        <v>22.36041584227171</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.443072657131192</v>
+        <v>0.1133755171239547</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.9664500508680502</v>
+        <v>-0.2008327611707117</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6510</v>
+        <v>6532</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>554.1657526892621</v>
+        <v>558.4811791798204</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2880</v>
+        <v>114</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>43.60565082008124</v>
+        <v>51.97413301480386</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>13.78977807966499</v>
+        <v>43.20706092143895</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.940496050486078</v>
+        <v>0.4128331156998558</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-25.50375776452532</v>
+        <v>-1.102100447244763</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6505</v>
+        <v>6667</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>546.8363850374226</v>
+        <v>555.8732405115766</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>257</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>47.39729661484663</v>
+        <v>49.50357593798491</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>49.51825358153283</v>
+        <v>27.98751796812688</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5041689005788424</v>
+        <v>0.2692725601225107</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-2.329543879256948</v>
+        <v>-2.761368836431115</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6706</v>
+        <v>6834</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>545.5049330508283</v>
+        <v>539.1968388893052</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>134.5</v>
+        <v>125</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>42.77592101180937</v>
+        <v>49.28907529042817</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>34.33289610108948</v>
+        <v>43.20715133039151</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5225165277174064</v>
+        <v>0.2728104723038061</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-2.292064146746896</v>
+        <v>-3.139393722327508</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6719</v>
+        <v>6655</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>535.0480896799882</v>
+        <v>537.0485057483463</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>190</v>
+        <v>138</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.84269493734669</v>
+        <v>54.2589825560043</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.13119743594272</v>
+        <v>9.618662058956716</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>4.376599059544187</v>
+        <v>0.5155808533894285</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,101 +1630,101 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.5179646447842252</v>
+        <v>1.33915074691202</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6806</v>
+        <v>6770</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>536.1904212300309</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>3.51</v>
+        <v>69.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>31.69497945321342</v>
+        <v>49.479499610093</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>32.59377512599728</v>
+        <v>11.53510472554859</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.013053626871307</v>
+        <v>1.107130066578089</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.4112804104174987</v>
+        <v>-0.006654498226614458</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6668</v>
+        <v>6806</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>527.0684104725617</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>54.2</v>
+        <v>3.51</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G24" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.46780470510702</v>
+        <v>31.69498236330794</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>42.96725784563373</v>
+        <v>32.59379748871298</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6845844437876953</v>
+        <v>2.013053626871307</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.8922843062466459</v>
+        <v>0.4112803877422957</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6485</v>
+        <v>6605</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>525.5993112503465</v>
+        <v>520.1478872588227</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>72.7</v>
+        <v>137</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>48.94284818224295</v>
+        <v>51.555150943002</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>25.51923772620657</v>
+        <v>9.049760822560444</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.1710417641704578</v>
+        <v>0.8258796823797766</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-1.187560854578068</v>
+        <v>0.06532515100251934</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6658</v>
+        <v>6695</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>517.3003407642074</v>
+        <v>516.3877852806575</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>181.5</v>
+        <v>53.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>44.74424198572068</v>
+        <v>55.1781995021331</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>35.33831462656354</v>
+        <v>23.48028621814434</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.285159871931107</v>
+        <v>0.8440539522246153</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-2.975350835011868</v>
+        <v>0.2258430187599103</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6548</v>
+        <v>6598</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>507.8489392724243</v>
+        <v>512.8397067344999</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>72.5</v>
+        <v>29.1</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>43.84203290056096</v>
+        <v>54.74626644579197</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.9098801550873</v>
+        <v>18.30500466697115</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.6650595247241324</v>
+        <v>0.979079369110421</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.9971818815225784</v>
+        <v>0.09883900791083172</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6667</v>
+        <v>6588</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>500.8732405115765</v>
+        <v>506.748575831626</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>257</v>
+        <v>88.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>49.50357600392523</v>
+        <v>35.02041864882507</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>27.98751795206534</v>
+        <v>26.4914111612952</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2692725601225107</v>
+        <v>0.3089412958147158</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-2.7613688381132</v>
+        <v>-1.366595517822896</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6805</v>
+        <v>6708</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>498.0326068975079</v>
+        <v>498.1548386911228</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2425</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.79369724568803</v>
+        <v>58.429092291669</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>25.84930353585029</v>
+        <v>25.50194432437306</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7390993123783484</v>
+        <v>2.443072657131192</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.2045176884032998</v>
+        <v>-0.9664500507559071</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6645</v>
+        <v>6510</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>489.0757879644201</v>
+        <v>494.1657526892621</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>13.4</v>
+        <v>2880</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.2696353790146</v>
+        <v>43.60565078403807</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>30.4778866982224</v>
+        <v>13.78977807989899</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.1222495374319416</v>
+        <v>1.940496050486078</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.07371208548937569</v>
+        <v>-25.50375772948312</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6716</v>
+        <v>6486</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>469.2346519184314</v>
+        <v>487.3810839180093</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>36.87302497074365</v>
+        <v>57.2314043831126</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23.25590736846222</v>
+        <v>31.91184210952488</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3592668651066209</v>
+        <v>0.5004257125598371</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-2.581167863079079</v>
+        <v>0.2409646578923315</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
+          <t>rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6584</v>
+        <v>6706</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>460.4872307642239</v>
+        <v>485.5049330508283</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>422</v>
+        <v>134.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,49 +2142,49 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>26.81370165254459</v>
+        <v>42.77592102901959</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>35.57771202512632</v>
+        <v>34.33289603054379</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.152987744534452</v>
+        <v>0.5225165277174064</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-6.386568061378526</v>
+        <v>-2.292064146606717</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6598</v>
+        <v>6546</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>457.8397067344997</v>
+        <v>474.8293852566974</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>29.1</v>
+        <v>60.6</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>54.74626616517162</v>
+        <v>51.6214913386224</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>18.30500424245174</v>
+        <v>11.17177112829199</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.979079369110421</v>
+        <v>1.158337807031876</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.09883900823322234</v>
+        <v>0.04310162889917235</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6655</v>
+        <v>6485</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>457.0485057483464</v>
+        <v>465.5993112503454</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>138</v>
+        <v>72.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.25898254658503</v>
+        <v>48.94284807897462</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>9.618662079060922</v>
+        <v>25.5192377843214</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5155808533894285</v>
+        <v>0.1710417641704578</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.339150747332539</v>
+        <v>-1.187560853540802</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6742</v>
+        <v>6674</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>446.2209509925164</v>
+        <v>465.5255260047516</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>58.9</v>
+        <v>18.3</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.24295501882862</v>
+        <v>65.76246001410465</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>47.64793857783743</v>
+        <v>46.99363719256134</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7466969749584867</v>
+        <v>0.5677365662612504</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.5829386916174366</v>
+        <v>-0.08970950104808961</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6743</v>
+        <v>6658</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>438.2376715397478</v>
+        <v>457.3003407642074</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>29.75</v>
+        <v>181.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>38.92039315770321</v>
+        <v>44.74424197538705</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>27.56094941731322</v>
+        <v>35.3383146560775</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.9717977824370764</v>
+        <v>0.285159871931107</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.4071260934110952</v>
+        <v>-2.97535083495581</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6486</v>
+        <v>6668</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>432.3810839180093</v>
+        <v>457.0684104725618</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>81.09999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.2314043564561</v>
+        <v>51.46780458917185</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>31.91184212540356</v>
+        <v>42.96725785835573</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5004257125598371</v>
+        <v>0.6845844437876953</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.2409646578923315</v>
+        <v>-0.8922843055878511</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6739</v>
+        <v>6548</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>419.9149078403549</v>
+        <v>447.8489392724243</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>875</v>
+        <v>72.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>35.46304453296415</v>
+        <v>43.84203290838036</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>20.10975308341932</v>
+        <v>21.90988017393443</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.013389792196378</v>
+        <v>0.6650595247241324</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-14.22665966701523</v>
+        <v>-0.9971818815085625</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6517</v>
+        <v>6789</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>418.8166193399468</v>
+        <v>445.8338300766127</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>67.3</v>
+        <v>438.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>47.49300163209622</v>
+        <v>44.53230087842917</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>25.89920703252025</v>
+        <v>15.56681136313345</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2816619339946828</v>
+        <v>0.4093864555843917</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.2831785826947062</v>
+        <v>-2.75117435274568</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6674</v>
+        <v>6582</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>415.5255260047516</v>
+        <v>434.1025557972103</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>18.3</v>
+        <v>31.65</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>65.76245992220187</v>
+        <v>51.96369159993993</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46.99363703722322</v>
+        <v>22.37023200722435</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5677365662612504</v>
+        <v>0.8381548542796053</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.08970950093595254</v>
+        <v>0.02387589579754075</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6550</v>
+        <v>6645</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>412.0404719957397</v>
+        <v>429.0757879644203</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>55.45574467508124</v>
+        <v>50.26963547577344</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>28.9093849616553</v>
+        <v>30.47788666911887</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2207582019340306</v>
+        <v>0.1222495374319416</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.2648157851527613</v>
+        <v>-0.07371208546134228</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6683</v>
+        <v>6716</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>400.8171192555358</v>
+        <v>409.2346519184314</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1135</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>35.52641833699795</v>
+        <v>36.8730249393045</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>19.16336566222174</v>
+        <v>23.25590737526988</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5039281628496418</v>
+        <v>0.3592668651066209</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-30.4734866051443</v>
+        <v>-2.581167863023012</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6534</v>
+        <v>6790</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>395.1337551712396</v>
+        <v>405.4696528087454</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>92</v>
+        <v>37.95</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>49.17774965188432</v>
+        <v>56.05869631015241</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>22.36041584227171</v>
+        <v>14.64163448204889</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.1133755171239547</v>
+        <v>0.5156662726772513</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.2008327622920705</v>
+        <v>0.06402611799280494</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6546</v>
+        <v>6533</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>394.8293852566974</v>
+        <v>401.8923009524889</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>60.6</v>
+        <v>285</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.62149116478381</v>
+        <v>47.57985197212099</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>11.17177111242463</v>
+        <v>20.62004614859488</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.158337807031876</v>
+        <v>0.8353222175981325</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.04310162889917235</v>
+        <v>-7.063358875225027</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6807</v>
+        <v>6585</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>383.2861671890712</v>
+        <v>401.2755135526858</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>33.95</v>
+        <v>95.2</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.18701361156501</v>
+        <v>36.74946333870756</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>8.01905195929338</v>
+        <v>41.30064132892989</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3293626832079926</v>
+        <v>0.3811522800793102</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.472200548993026</v>
+        <v>-0.1493137762903052</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6525</v>
+        <v>6584</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>380.0189682578838</v>
+        <v>400.4872307642238</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>117</v>
+        <v>422</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,49 +2884,49 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>33.90937419607231</v>
+        <v>26.81370160864829</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20.95288361680378</v>
+        <v>35.57771205378631</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5047111905615824</v>
+        <v>1.152987744534452</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.697125667286246</v>
+        <v>-6.386568060537527</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6582</v>
+        <v>6592</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>379.1025557972109</v>
+        <v>395.7919527307805</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>31.65</v>
+        <v>56.9</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.96369169293634</v>
+        <v>43.86723059097354</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.37023204274836</v>
+        <v>23.38618420297316</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.8381548542796053</v>
+        <v>0.551058046486896</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.02387589581155914</v>
+        <v>0.1450769380320212</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6693</v>
+        <v>6671</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>367.3008495603935</v>
+        <v>393.2066846792516</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>160.5</v>
+        <v>23.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>38.0342139032061</v>
+        <v>57.511397034299</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>21.06022358945772</v>
+        <v>12.92723380407791</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2844684271173948</v>
+        <v>1.298185741752818</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-3.761980866058203</v>
+        <v>0.04310032327559695</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6761</v>
+        <v>6720</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>365.7745495320991</v>
+        <v>392.3463095890036</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>144</v>
+        <v>104.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>31.070072896916</v>
+        <v>43.38529447081672</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>29.44922764063622</v>
+        <v>18.60949067308864</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7341702457289206</v>
+        <v>1.310677092688612</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-1.142162058892473</v>
+        <v>-0.01820725889028019</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6691</v>
+        <v>6742</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>363.7561102033164</v>
+        <v>386.2209509925161</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>649</v>
+        <v>58.9</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>41.27013571132285</v>
+        <v>53.24295498885856</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>24.11645615220792</v>
+        <v>47.64793859093744</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.281449557452308</v>
+        <v>0.7466969749584867</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-11.68833319900184</v>
+        <v>-0.5829386917295745</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6790</v>
+        <v>6743</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>350.4696528087453</v>
+        <v>378.2376715397478</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>37.95</v>
+        <v>29.75</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>56.05869634175421</v>
+        <v>38.92039296202448</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.64163437353707</v>
+        <v>27.56094945601671</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5156662726772513</v>
+        <v>0.9717977824370764</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.06402611800682102</v>
+        <v>-0.4071260929905883</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6725</v>
+        <v>6781</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>349.8017908434022</v>
+        <v>374.1014150671712</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>176</v>
+        <v>907</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>26.9348754980539</v>
+        <v>35.40333813836781</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>25.9778483357326</v>
+        <v>30.46447743190542</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.240668930243489</v>
+        <v>0.6374652497066527</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>3</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.917168151036551</v>
+        <v>-5.056280091909404</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6533</v>
+        <v>6624</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>346.8923009524889</v>
+        <v>368.8992142784826</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>285</v>
+        <v>34.8</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>47.57985202892563</v>
+        <v>51.45392584315253</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>20.62004626101508</v>
+        <v>8.304343181272335</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8353222175981325</v>
+        <v>1.848385955254984</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-7.0633588787293</v>
+        <v>0.6350664280751972</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6692</v>
+        <v>6614</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>346.7347873570217</v>
+        <v>362.4326802055011</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>22.55</v>
+        <v>35.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.94299619984873</v>
+        <v>54.79500996103916</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>5.5654599830722</v>
+        <v>20.13910059719066</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.62315207707292</v>
+        <v>0.5916804406223032</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.05264091593055167</v>
+        <v>0.08633814422056796</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6605</v>
+        <v>6739</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>345.1478872588227</v>
+        <v>359.9149078403548</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>137</v>
+        <v>875</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.55515099641885</v>
+        <v>35.46304470821055</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>9.049760822560446</v>
+        <v>20.1097530962441</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8258796823797766</v>
+        <v>1.013389792196378</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.06532515114268994</v>
+        <v>-14.22665966869717</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6654</v>
+        <v>6517</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>343.2084291742079</v>
+        <v>358.8166193399468</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>202</v>
+        <v>67.3</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.89478845020003</v>
+        <v>47.49300160496455</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.12683524100844</v>
+        <v>25.89920706415576</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.2390413524762533</v>
+        <v>0.2816619339946828</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-1.88484237139577</v>
+        <v>-0.2831785826947062</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6592</v>
+        <v>6792</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>340.7919527307805</v>
+        <v>354.384035664847</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>56.9</v>
+        <v>58.1</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>43.86723066088646</v>
+        <v>43.00732022408495</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>23.38618405272754</v>
+        <v>33.10513244040492</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.551058046486896</v>
+        <v>0.4211820565979739</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1450769380320212</v>
+        <v>-0.2046534114373077</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6670</v>
+        <v>6550</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>340.1495302702558</v>
+        <v>352.0404719957397</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>262.5</v>
+        <v>15.2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>41.25429980821821</v>
+        <v>55.45574487360754</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>12.50733765206599</v>
+        <v>28.90938470490481</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4319991455992198</v>
+        <v>0.2207582019340306</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.01431831652578</v>
+        <v>-0.2648157853084641</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>rsi_strong, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6671</v>
+        <v>6560</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>338.2066846792516</v>
+        <v>342.2365317745105</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>23.5</v>
+        <v>34.05</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>57.51137157462871</v>
+        <v>58.47548114018919</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>12.927236998507</v>
+        <v>13.75769740793604</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.298185741752818</v>
+        <v>1.047149630807521</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.04310033366218215</v>
+        <v>0.1321034029664339</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6579</v>
+        <v>6683</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>337.0565268056164</v>
+        <v>340.8171192555357</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>138</v>
+        <v>1135</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>30.2891057171569</v>
+        <v>35.52641828632265</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>32.30353316231744</v>
+        <v>19.16336568651716</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7241950164990085</v>
+        <v>0.5039281628496418</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-1.162945033853363</v>
+        <v>-30.47348660051885</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6530</v>
+        <v>6829</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>334.4015141393378</v>
+        <v>323.5160394132097</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>87.40000000000001</v>
+        <v>195.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>41.60275253982503</v>
+        <v>42.9721215414506</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.81580820182782</v>
+        <v>10.80280668517597</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3386752246297662</v>
+        <v>0.3834372927101594</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.184769939073705</v>
+        <v>0.3084804704034223</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6831</v>
+        <v>6641</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>329.9838694655467</v>
+        <v>321.8602178769436</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>388</v>
+        <v>16.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>27.8820139602617</v>
+        <v>49.86845096885047</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>38.32841403033775</v>
+        <v>9.774655210917294</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3640727727171815</v>
+        <v>2.589390161149989</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.981186544594479</v>
+        <v>-0.01300451368297784</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, avoid_chase, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6570</v>
+        <v>6830</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>327.9648614562329</v>
+        <v>320.8889277718354</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>45.45</v>
+        <v>482</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>34.71494173689668</v>
+        <v>44.20331582738062</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.13545593955636</v>
+        <v>19.54305175702343</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5301733992368501</v>
+        <v>0.7169846880697807</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.01645514763683897</v>
+        <v>-3.939069199804308</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6781</v>
+        <v>6525</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>324.1014150671713</v>
+        <v>320.0189682578841</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>907</v>
+        <v>117</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>35.40333849860968</v>
+        <v>33.90937421526998</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>30.46447713663195</v>
+        <v>20.95288346763964</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6374652497066527</v>
+        <v>0.5047111905615824</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-5.05628012555016</v>
+        <v>-1.69712566720213</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6556</v>
+        <v>6625</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>321.215120867291</v>
+        <v>313.0406528986429</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>62.3</v>
+        <v>73</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48.04894654239791</v>
+        <v>43.77959356742565</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>32.10478967351426</v>
+        <v>15.04105129049205</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4697729228236879</v>
+        <v>0.4352536227006117</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1636366620146121</v>
+        <v>0.03224221229586388</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6776</v>
+        <v>6693</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>321.1038151713077</v>
+        <v>307.3008495603935</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>52.8</v>
+        <v>160.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.15505837597295</v>
+        <v>38.03421387118453</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>10.18968221856955</v>
+        <v>21.06022349313091</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3498308598908769</v>
+        <v>0.2844684271173948</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.04355104198938691</v>
+        <v>-3.761980865777878</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6720</v>
+        <v>6761</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>312.3463095890035</v>
+        <v>305.7745495320984</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>104.5</v>
+        <v>144</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>43.38529442322076</v>
+        <v>31.07007274981068</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.60949064191275</v>
+        <v>29.44922768048884</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.310677092688612</v>
+        <v>0.7341702457289206</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.01820725903045073</v>
+        <v>-1.142162058191618</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, above_ichimoku_cloud</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6770</v>
+        <v>6796</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>311.1904212300308</v>
+        <v>304.7548122270102</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>69.5</v>
+        <v>53</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.47949960443455</v>
+        <v>46.36257185861144</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>11.53510472656572</v>
+        <v>17.5800958617552</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.107130066578089</v>
+        <v>1.255701505989246</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.00665449832473497</v>
+        <v>-0.1558256187393194</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6589</v>
+        <v>6606</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>306.9179643614542</v>
+        <v>304.2732198447911</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>49</v>
+        <v>24.85</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>46.14379195548912</v>
+        <v>51.19999594718149</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.56814389530745</v>
+        <v>22.55418643616764</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.879477659376803</v>
+        <v>0.3516672548266023</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.2464424606441291</v>
+        <v>0.1133888426807164</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6504</v>
+        <v>6691</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>306.6447602172357</v>
+        <v>303.7561102033164</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>36.5</v>
+        <v>649</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>42.5877671917478</v>
+        <v>41.27013561876657</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>43.12386037674244</v>
+        <v>24.11645606521227</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2113905144662769</v>
+        <v>0.281449557452308</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.3488361656474696</v>
+        <v>-11.68833319507711</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6792</v>
+        <v>6754</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>304.3840356648535</v>
+        <v>296.5478095900732</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>58.1</v>
+        <v>40.35</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>43.00731958900943</v>
+        <v>42.22340599349685</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>33.10513203242303</v>
+        <v>14.25623715303691</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4211820565979739</v>
+        <v>0.634384932089093</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.2046534099515098</v>
+        <v>-0.05523486771864683</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6669</v>
+        <v>6515</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>302.8252089116323</v>
+        <v>293.6494280916041</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1885</v>
+        <v>4655</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>31.68147581106551</v>
+        <v>33.28413301310114</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>40.80791153982742</v>
+        <v>19.0316384124566</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7558439956723754</v>
+        <v>0.847878742237447</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>77.92173934594638</v>
+        <v>-51.59393166022517</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6651</v>
+        <v>6725</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>301.8501563082349</v>
+        <v>289.8017908434022</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>139.5</v>
+        <v>176</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45.28610272259074</v>
+        <v>26.93487581449776</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11.14651667805856</v>
+        <v>25.97784833573261</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.2342702541262743</v>
+        <v>1.240668930243489</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>3</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.6877123802863137</v>
+        <v>-1.917168151036551</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6741</v>
+        <v>6692</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>283.1887992850911</v>
+        <v>286.7347873570217</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>48.45</v>
+        <v>22.55</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>28.11099917773554</v>
+        <v>50.94299626296704</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.23534188962304</v>
+        <v>5.565459983072199</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.876881926086464</v>
+        <v>1.62315207707292</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.3740852287656757</v>
+        <v>-0.05264091588849984</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6803</v>
+        <v>6799</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>282.793746507166</v>
+        <v>286.7180552668875</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>261</v>
+        <v>83.3</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>40.02737585552938</v>
+        <v>45.53801018375659</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>25.28691939295679</v>
+        <v>23.23273090753209</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.535790935943937</v>
+        <v>0.3917806115775486</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.07718182075474722</v>
+        <v>-0.7214747147011065</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6488</v>
+        <v>6531</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>278.4787193286705</v>
+        <v>283.304347679593</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>814</v>
+        <v>841</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>36.25542216933822</v>
+        <v>43.89801286081453</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>22.85123693177342</v>
+        <v>18.43009697207251</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.5478719328670507</v>
+        <v>0.6954722517618525</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-25.79345247061223</v>
+        <v>-10.48636064383297</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6641</v>
+        <v>6654</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>271.8602178769436</v>
+        <v>283.2084291742078</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>16.9</v>
+        <v>202</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.86845098466552</v>
+        <v>48.8947884244155</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>9.774655203090521</v>
+        <v>20.12683533712596</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>2.589390161149989</v>
+        <v>0.2390413524762533</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.01300451368297784</v>
+        <v>-1.884842371031349</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6829</v>
+        <v>6776</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>268.5160394132097</v>
+        <v>281.1038151713077</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>195.5</v>
+        <v>52.8</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.97212153560039</v>
+        <v>51.15505869199605</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10.80280665268999</v>
+        <v>10.18968213368249</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3834372927101594</v>
+        <v>0.3498308598908769</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3084804709641098</v>
+        <v>0.04355104159691014</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6830</v>
+        <v>6670</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>265.8889277718354</v>
+        <v>280.1495302702556</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>482</v>
+        <v>262.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.20331580473842</v>
+        <v>41.25429971801078</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.5430516933667</v>
+        <v>12.50733764321884</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.7169846880697807</v>
+        <v>0.4319991455992198</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-3.939069198823161</v>
+        <v>-1.014318316946308</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6494</v>
+        <v>6579</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>265.1252138599245</v>
+        <v>277.0565268056164</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>46.2</v>
+        <v>138</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>32.58289992198885</v>
+        <v>30.28910563117937</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20.05250515951844</v>
+        <v>32.3035332012207</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.8708441651242275</v>
+        <v>0.7241950164990085</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.2564593056091868</v>
+        <v>-1.162945033573039</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6512</v>
+        <v>6530</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>262.7812871723837</v>
+        <v>274.4015141393378</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>36.85332812669809</v>
+        <v>41.60275255265996</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7.951423527934907</v>
+        <v>18.8158082511168</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.03319738927318748</v>
+        <v>0.3386752246297662</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.9509305544830944</v>
+        <v>-1.184769938793363</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6597</v>
+        <v>6831</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>250.9450747087479</v>
+        <v>269.9838694655466</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>66.3</v>
+        <v>388</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.64541336438912</v>
+        <v>27.88201389391342</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>7.263083107181699</v>
+        <v>38.32841420075377</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.8713647750789675</v>
+        <v>0.3640727727171815</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1.368671143715996</v>
+        <v>-2.981186541931208</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6789</v>
+        <v>6570</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>250.8338300766107</v>
+        <v>267.9648614562329</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>438.5</v>
+        <v>45.45</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>44.53230089214848</v>
+        <v>34.71494262732453</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.5668114089876</v>
+        <v>23.13545589323131</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4093864555843917</v>
+        <v>0.5301733992368501</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-2.751174360314847</v>
+        <v>0.01645514774897672</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6568</v>
+        <v>6556</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>250.5668605944538</v>
+        <v>261.215120867291</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>129.5</v>
+        <v>62.3</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>43.07212296960637</v>
+        <v>48.04894659523507</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.21567545434395</v>
+        <v>32.10478981482829</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4332391238819467</v>
+        <v>0.4697729228236879</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.5425086334162927</v>
+        <v>-0.1636366619585447</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6515</v>
+        <v>6722</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>243.6494280916041</v>
+        <v>258.5371451616649</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>4655</v>
+        <v>32.4</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>33.28413309156217</v>
+        <v>44.59710365414917</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>19.03163847366286</v>
+        <v>34.50098357035877</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.847878742237447</v>
+        <v>0.4691667170896769</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-51.59393170367764</v>
+        <v>-0.06350205982566995</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6585</v>
+        <v>6669</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>236.2755135526858</v>
+        <v>252.8252089116323</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>95.2</v>
+        <v>1885</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>36.7494631094609</v>
+        <v>31.68147582161389</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>41.30064133513714</v>
+        <v>40.8079115570569</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3811522800793102</v>
+        <v>0.7558439956723754</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1493137761501329</v>
+        <v>77.92173937117656</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6560</v>
+        <v>6680</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>232.2365317745104</v>
+        <v>247.3077823480866</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>34.05</v>
+        <v>56.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>58.47548103811268</v>
+        <v>53.20899735115141</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.75769737608811</v>
+        <v>6.081007478385286</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.047149630807521</v>
+        <v>1.630778234808655</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1321034031486529</v>
+        <v>1.405471484402879</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, above_ichimoku_cloud</t>
+          <t>volume_break, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6624</v>
+        <v>6589</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>228.8992142784826</v>
+        <v>246.9179643614543</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>34.8</v>
+        <v>49</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.453925839757</v>
+        <v>46.14379192730411</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>8.304343181272337</v>
+        <v>15.56814397193015</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.848385955254984</v>
+        <v>0.879477659376803</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>1</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.6350664280471632</v>
+        <v>-0.2464424601114817</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6606</v>
+        <v>6504</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>224.2732198447912</v>
+        <v>246.6447602172357</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>24.85</v>
+        <v>36.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>51.19999591451218</v>
+        <v>42.58776706538641</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.55418631651228</v>
+        <v>43.12386045972216</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3516672548266023</v>
+        <v>0.2113905144662769</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1133888427648175</v>
+        <v>-0.3488361653951626</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6577</v>
+        <v>6651</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>223.3769043673649</v>
+        <v>241.850156308235</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>78.2</v>
+        <v>139.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>39.06218554681152</v>
+        <v>45.28610265821808</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>9.268875038460594</v>
+        <v>11.14651666992998</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5494638381749638</v>
+        <v>0.2342702541262743</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.193235461526042</v>
+        <v>-0.6877123802863137</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6664</v>
+        <v>6474</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>222.1264148924457</v>
+        <v>227.2869680163046</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>328</v>
+        <v>35.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>37.47436938247828</v>
+        <v>46.38001447995574</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.83459017570794</v>
+        <v>12.59489244586729</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3575835579600932</v>
+        <v>0.4888013572384353</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-4.327291469613639</v>
+        <v>0.07355107206320671</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6788</v>
+        <v>6741</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>212.3196980875435</v>
+        <v>223.188799285091</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>341</v>
+        <v>48.45</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>44.89414761622088</v>
+        <v>28.1109991899867</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.8463869361435</v>
+        <v>45.23534188884003</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4376480432734589</v>
+        <v>0.876881926086464</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-2.92332616912683</v>
+        <v>-0.3740852286255081</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6799</v>
+        <v>6803</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>211.7180552668875</v>
+        <v>222.7937465071663</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>83.3</v>
+        <v>261</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.53801018375659</v>
+        <v>40.02737610400622</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>23.2327309597727</v>
+        <v>25.28691930498981</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3917806115775486</v>
+        <v>1.535790935943937</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.7214747145889745</v>
+        <v>0.07718182089496706</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6640</v>
+        <v>6757</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>209.1944299518906</v>
+        <v>221.966008835062</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>940</v>
+        <v>52.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.565569233509</v>
+        <v>41.69636244484169</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15.23075714864725</v>
+        <v>13.31358906228933</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3163022959567353</v>
+        <v>0.5104140868260776</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-11.9633658921104</v>
+        <v>-0.0503003269154414</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6642</v>
+        <v>6488</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>204.0228734643207</v>
+        <v>218.4787193286705</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>71.8</v>
+        <v>814</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>36.72228655116781</v>
+        <v>36.25542218139168</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>18.43313495267936</v>
+        <v>22.85123678228211</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5990471359603431</v>
+        <v>0.5478719328670507</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.4912518982496898</v>
+        <v>-25.79345247033189</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6722</v>
+        <v>6666</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>203.5371451616649</v>
+        <v>205.826327424678</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>32.4</v>
+        <v>41.55</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.59710442082165</v>
+        <v>40.44693012961302</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>34.50098355658177</v>
+        <v>26.79846778704922</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4691667170896769</v>
+        <v>1.065626963429644</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.06350205985370497</v>
+        <v>-0.1096040019660418</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6531</v>
+        <v>6494</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>203.304347679593</v>
+        <v>205.1252138599257</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>841</v>
+        <v>46.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.8980128656772</v>
+        <v>32.58289994571219</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>18.43009700463947</v>
+        <v>20.05250507950708</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6954722517618525</v>
+        <v>0.8708441651242275</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-10.48636064551508</v>
+        <v>-0.2564593059175579</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6643</v>
+        <v>6512</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>194.6322433115018</v>
+        <v>202.7812871723837</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>436.5</v>
+        <v>0</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>44.7332605291454</v>
+        <v>36.85332812774302</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.17867553952977</v>
+        <v>7.95142352736567</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4435571414058808</v>
+        <v>0.03319738927318748</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-5.937617264967211</v>
+        <v>-0.9509305545111263</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6753</v>
+        <v>6768</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>189.9228253645828</v>
+        <v>201.2027444181211</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>120</v>
+        <v>63.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>29.88216617983926</v>
+        <v>49.44378874769804</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>28.2619471623178</v>
+        <v>19.45760670039175</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6956633372237513</v>
+        <v>0.5935652334405705</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.3187285621240017</v>
+        <v>-0.0307945829853595</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6823</v>
+        <v>6597</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>189.5968872204897</v>
+        <v>190.945074708748</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>57.5</v>
+        <v>66.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.12034188010277</v>
+        <v>51.64541336996755</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>22.61876178833202</v>
+        <v>7.263083107504813</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.02211420375984404</v>
+        <v>0.8713647750789675</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.3325982500755067</v>
+        <v>1.368671143603862</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6591</v>
+        <v>6568</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>185.6351933442451</v>
+        <v>190.5668605944553</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>40</v>
+        <v>129.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>34.09947602121105</v>
+        <v>43.07212301656364</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>22.63290932912732</v>
+        <v>13.21567551742975</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.4278486488916107</v>
+        <v>0.4332391238819467</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.2423830829029214</v>
+        <v>-0.5425086336966394</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6498</v>
+        <v>6794</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>173.0451331955394</v>
+        <v>169.8452613978606</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>62.6</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>35.13635655490857</v>
+        <v>36.9440223657578</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.55975443115532</v>
+        <v>14.73806283849732</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5981334294517382</v>
+        <v>0.2482452255150714</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.5631863696546513</v>
+        <v>-0.1167607640532813</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6614</v>
+        <v>6577</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>172.4326802055012</v>
+        <v>163.3769043673648</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>35.6</v>
+        <v>78.2</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>54.79500901180981</v>
+        <v>39.06218562099104</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>20.13910067750299</v>
+        <v>9.268874989538023</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5916804406223032</v>
+        <v>0.5494638381749638</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.08633814433270359</v>
+        <v>-0.193235461722269</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6474</v>
+        <v>6664</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>172.2869680163046</v>
+        <v>162.126414892446</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>35.5</v>
+        <v>328</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>46.38001381252898</v>
+        <v>37.47436938247828</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.59489224302524</v>
+        <v>18.83459021643568</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4888013572384353</v>
+        <v>0.3575835579600932</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.07355107259585797</v>
+        <v>-4.32729146821198</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6573</v>
+        <v>6788</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>170.7830205569375</v>
+        <v>152.3196980875425</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14.5</v>
+        <v>341</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>30.81081982320782</v>
+        <v>44.89414766451403</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14.13995681986816</v>
+        <v>14.84638693889308</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5033346297847193</v>
+        <v>0.4376480432734589</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.06730007031228474</v>
+        <v>-2.923326169827709</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6657</v>
+        <v>6640</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>170.2073749944447</v>
+        <v>149.1944299518906</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>32.6</v>
+        <v>940</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.64145423717849</v>
+        <v>40.56556934204678</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>23.8767914457472</v>
+        <v>15.23075716204002</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.7897467607051948</v>
+        <v>0.3163022959567353</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1341466153335462</v>
+        <v>-11.96336588734458</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6666</v>
+        <v>6591</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>155.826327424678</v>
+        <v>145.6351933442525</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>41.55</v>
+        <v>40</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.44693004026475</v>
+        <v>34.09947592807131</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>26.79846775069268</v>
+        <v>22.63290927007205</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.065626963429644</v>
+        <v>0.4278486488916107</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1096040017698037</v>
+        <v>-0.2423830828188219</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6558</v>
+        <v>6642</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>151.6722163751841</v>
+        <v>144.0228734643207</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>23.3</v>
+        <v>71.8</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.29658537841117</v>
+        <v>36.72228653001525</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>21.15193943066712</v>
+        <v>18.433134905187</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.222919850434152</v>
+        <v>0.5990471359603431</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1125579007166652</v>
+        <v>-0.4912518982216514</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6541</v>
+        <v>6698</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>148.7392061384955</v>
+        <v>137.3291258251724</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.02486874741586</v>
+        <v>41.19005425193105</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.33223487863988</v>
+        <v>9.795117394916591</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.3525190601949399</v>
+        <v>0.7353471836699833</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.02513151152551307</v>
+        <v>-0.07444096480985685</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6625</v>
+        <v>6643</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>148.0406528986429</v>
+        <v>134.632243311502</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>73</v>
+        <v>436.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.77959331625431</v>
+        <v>44.7332605642415</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.04105110322936</v>
+        <v>17.1786756692326</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4352536227006117</v>
+        <v>0.4435571414058808</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.03224221240799219</v>
+        <v>-5.937617266649298</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6757</v>
+        <v>6573</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>146.9660088350617</v>
+        <v>130.7830205569378</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>52.3</v>
+        <v>14.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.69636235932956</v>
+        <v>30.8108198036327</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13.31358892472231</v>
+        <v>14.13995680447621</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5104140868260776</v>
+        <v>0.5033346297847193</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.05030032713970894</v>
+        <v>-0.06730007031228474</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6771</v>
+        <v>6753</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>141.5198215124763</v>
+        <v>129.9228253645816</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>39.65</v>
+        <v>120</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>33.25093836977925</v>
+        <v>29.88216625476956</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.60482563946201</v>
+        <v>28.26194747602747</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.1162630356548989</v>
+        <v>0.6956633372237513</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.2134122244198869</v>
+        <v>-0.3187285603018033</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6796</v>
+        <v>6823</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>139.7548122270102</v>
+        <v>129.5968872204894</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>53</v>
+        <v>57.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.36257181039488</v>
+        <v>42.1203419281648</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.58009583154313</v>
+        <v>22.61876179824937</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.255701505989246</v>
+        <v>0.02211420375984404</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1558256184309454</v>
+        <v>-0.3325982498792739</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6754</v>
+        <v>6552</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>131.5478095900732</v>
+        <v>123.7426544255196</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>40.35</v>
+        <v>22.8</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.22340594454693</v>
+        <v>37.55944298908322</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.25623705803061</v>
+        <v>16.35666142366389</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.634384932089093</v>
+        <v>1.225439662665299</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.05523486787283194</v>
+        <v>-0.09374671896354136</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6768</v>
+        <v>6498</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>126.2027444181207</v>
+        <v>113.0451331955394</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>63.4</v>
+        <v>62.6</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>49.44378907340107</v>
+        <v>35.13635674775877</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.45760674496005</v>
+        <v>13.55975437962794</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5935652334405705</v>
+        <v>0.5981334294517382</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.03079458340586302</v>
+        <v>-0.5631863692341443</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6794</v>
+        <v>6558</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>119.8452613978607</v>
+        <v>111.6722163751787</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>23.3</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>36.94402241463028</v>
+        <v>43.29658492166931</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>14.73806281753011</v>
+        <v>21.15193938378614</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2482452255150714</v>
+        <v>1.222919850434152</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.1167607641093416</v>
+        <v>-0.1125579001840213</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6763</v>
+        <v>6657</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>118.1275512159732</v>
+        <v>110.2073749944447</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>40.05</v>
+        <v>32.6</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>35.74539115742888</v>
+        <v>46.64145418230889</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13.60854655105929</v>
+        <v>23.87679144881063</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5899559818746294</v>
+        <v>0.7897467607051948</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.1139129432919535</v>
+        <v>-0.1341466153055111</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6680</v>
+        <v>6541</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>107.3077823480866</v>
+        <v>108.7392061384955</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>56.7</v>
+        <v>29.9</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>53.20899776675677</v>
+        <v>42.02486886801051</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>6.081007464955119</v>
+        <v>12.3322347672221</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.630778234808655</v>
+        <v>0.3525190601949399</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>1.405471484346809</v>
+        <v>-0.02513151183389006</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, above_ichimoku_cloud</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6821</v>
+        <v>6771</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>104.5679599797656</v>
+        <v>81.51982151247635</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>41.1</v>
+        <v>39.65</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>43.15277053836916</v>
+        <v>33.25093848378104</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.33030625552036</v>
+        <v>18.60482560467297</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.1558712227280364</v>
+        <v>0.1162630356548989</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.4568779972145017</v>
+        <v>-0.2134122243077487</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6732</v>
+        <v>6763</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>100.4586280047714</v>
+        <v>58.12755121598094</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>148.5</v>
+        <v>40.05</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>45.04016403920517</v>
+        <v>35.74539108044648</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>14.78620177730186</v>
+        <v>13.60854658246477</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5764761779485642</v>
+        <v>0.5899559818746294</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.2698178558572115</v>
+        <v>-0.1139129431798169</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6477</v>
+        <v>6821</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>94.8099519655311</v>
+        <v>44.56795997976955</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>31.05</v>
+        <v>41.1</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>34.43756030593899</v>
+        <v>43.15277055206943</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>16.12429050763114</v>
+        <v>19.33030620258041</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6705008718709836</v>
+        <v>0.1558712227280364</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.13247458963492</v>
+        <v>-0.4568779972285171</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6679</v>
+        <v>6732</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>89.52724319587058</v>
+        <v>40.45862800477105</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>185.5</v>
+        <v>148.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>38.62546610327905</v>
+        <v>45.04016532805601</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>19.69791702793508</v>
+        <v>14.78620171670515</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.2819019821843427</v>
+        <v>0.5764761779485642</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.5604896634701984</v>
+        <v>-0.2698178580999293</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6552</v>
+        <v>6477</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>88.74265442551959</v>
+        <v>34.80995196553098</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>22.8</v>
+        <v>31.05</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>37.55944294902136</v>
+        <v>34.43756040834661</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>16.35666142248619</v>
+        <v>16.12429055694708</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.225439662665299</v>
+        <v>0.6705008718709836</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.09374671892148889</v>
+        <v>-0.1324745897470572</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6698</v>
+        <v>6679</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>87.32912582517243</v>
+        <v>29.52724319587083</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>30.2</v>
+        <v>185.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>41.19005408783165</v>
+        <v>38.62546634149052</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>9.795117110186505</v>
+        <v>19.69791706075978</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.7353471836699833</v>
+        <v>0.2819019821843427</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,11 +7036,11 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.07444096493600966</v>
+        <v>-0.5604896627693492</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
@@ -7057,7 +7057,7 @@
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>85.38911246401454</v>
+        <v>25.38911246401428</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>55.6</v>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>32.58248413012136</v>
+        <v>32.58248403852589</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>14.05322150379487</v>
+        <v>14.05322143714209</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>1.034851307137162</v>
@@ -7089,11 +7089,11 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.5106677972108433</v>
+        <v>-0.5106677970706783</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>56.42126746225051</v>
+        <v>-3.578732537749649</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>45.9</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>44.71067793811645</v>
+        <v>44.71067774188393</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>16.4853184476636</v>
+        <v>16.48531846199897</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>0.2771097429503659</v>
@@ -7142,11 +7142,11 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1529677488338102</v>
+        <v>-0.1529677483572292</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
